--- a/data/trans_dic/P36B08_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36B08_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,06; 75,88</t>
+          <t>69,01; 75,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,11; 78,76</t>
+          <t>72,61; 79,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,69; 77,47</t>
+          <t>70,5; 77,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92,14; 96,68</t>
+          <t>92,81; 96,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,65; 80,68</t>
+          <t>74,59; 80,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,16; 85,18</t>
+          <t>79,67; 85,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,4; 78,98</t>
+          <t>72,32; 78,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>94,5; 97,05</t>
+          <t>94,54; 97,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73,06; 77,33</t>
+          <t>72,77; 77,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76,93; 81,31</t>
+          <t>76,88; 81,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72,25; 77,35</t>
+          <t>72,44; 77,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,04; 96,5</t>
+          <t>94,41; 96,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,92; 65,02</t>
+          <t>59,22; 65,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,82; 73,64</t>
+          <t>67,86; 73,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,06; 74,87</t>
+          <t>68,89; 74,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94,19; 98,05</t>
+          <t>93,89; 96,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,78; 71,8</t>
+          <t>65,31; 71,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,51; 79,89</t>
+          <t>74,57; 79,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,84; 79,23</t>
+          <t>73,97; 79,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>96,01; 97,92</t>
+          <t>96,23; 98,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,12; 67,79</t>
+          <t>63,25; 67,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72,02; 76,07</t>
+          <t>71,88; 76,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,34; 76,13</t>
+          <t>72,3; 76,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,36; 97,69</t>
+          <t>95,4; 97,17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,25; 62,02</t>
+          <t>54,13; 61,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,47; 69,74</t>
+          <t>62,2; 69,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,91; 70,03</t>
+          <t>62,79; 70,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89,57; 94,72</t>
+          <t>90,7; 95,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,84; 73,72</t>
+          <t>67,21; 74,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71,22; 77,73</t>
+          <t>71,39; 77,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,69; 76,25</t>
+          <t>69,44; 76,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92,45; 97,79</t>
+          <t>91,53; 95,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,74; 66,97</t>
+          <t>61,78; 66,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,83; 72,93</t>
+          <t>67,86; 72,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67,19; 72,16</t>
+          <t>67,45; 72,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91,94; 95,96</t>
+          <t>91,91; 94,77</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,25; 64,54</t>
+          <t>58,03; 64,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,36; 75,18</t>
+          <t>69,45; 75,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,13; 78,69</t>
+          <t>72,94; 78,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91,25; 94,95</t>
+          <t>91,58; 95,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,15; 71,95</t>
+          <t>66,2; 71,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,01; 85,92</t>
+          <t>80,82; 85,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,96; 84,81</t>
+          <t>80,26; 84,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94,34; 96,8</t>
+          <t>94,16; 96,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63,29; 67,57</t>
+          <t>63,43; 67,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76,13; 79,9</t>
+          <t>76,32; 80,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77,58; 81,36</t>
+          <t>77,68; 81,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,44; 95,65</t>
+          <t>93,56; 95,52</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,48; 64,97</t>
+          <t>61,68; 64,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,51; 72,71</t>
+          <t>69,56; 72,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70,75; 73,79</t>
+          <t>70,84; 73,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93,31; 95,72</t>
+          <t>93,49; 95,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>69,3; 72,52</t>
+          <t>69,41; 72,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,13; 80,83</t>
+          <t>78,08; 80,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,06; 78,81</t>
+          <t>75,86; 78,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>95,18; 96,74</t>
+          <t>95,08; 96,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66,1; 68,46</t>
+          <t>65,9; 68,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74,36; 76,5</t>
+          <t>74,4; 76,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,82; 75,98</t>
+          <t>73,76; 75,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>94,43; 95,93</t>
+          <t>94,46; 95,57</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>601422</t>
+          <t>656036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>647120</t>
+          <t>703056</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1248543</t>
+          <t>1359093</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>479275; 526638</t>
+          <t>478908; 525346</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>506476; 553239</t>
+          <t>509983; 555066</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>474124; 519635</t>
+          <t>472883; 521837</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>583875; 612637</t>
+          <t>639348; 666732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>513869; 555386</t>
+          <t>513455; 555254</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>551780; 593775</t>
+          <t>555349; 595446</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>485009; 529148</t>
+          <t>484529; 527584</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>637591; 654766</t>
+          <t>691987; 711097</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1009956; 1069019</t>
+          <t>1005945; 1066790</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1076529; 1137825</t>
+          <t>1075873; 1140118</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>968622; 1037002</t>
+          <t>971145; 1035567</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1230393; 1262524</t>
+          <t>1341398; 1373087</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1145511</t>
+          <t>1000994</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>928285</t>
+          <t>1039171</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2073796</t>
+          <t>2040164</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>566696; 625335</t>
+          <t>569547; 630257</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>687590; 746587</t>
+          <t>687982; 748147</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>705329; 764659</t>
+          <t>703590; 765651</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1122759; 1168799</t>
+          <t>983845; 1014239</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>636283; 694584</t>
+          <t>631740; 693756</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>766801; 822099</t>
+          <t>767422; 822843</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>769328; 825388</t>
+          <t>770628; 825948</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>917999; 936260</t>
+          <t>1028473; 1048031</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1217613; 1307838</t>
+          <t>1220195; 1306024</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1471352; 1554115</t>
+          <t>1468585; 1552810</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1492545; 1570760</t>
+          <t>1491741; 1570648</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2048503; 2098684</t>
+          <t>2019255; 2056696</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652569</t>
+          <t>747326</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>886008</t>
+          <t>762681</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1538576</t>
+          <t>1510007</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>368063; 420817</t>
+          <t>367276; 417648</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>471980; 526914</t>
+          <t>469940; 524501</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>471440; 524767</t>
+          <t>470501; 526654</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>631176; 667489</t>
+          <t>728395; 763769</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>457074; 504115</t>
+          <t>459624; 506621</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>552770; 603311</t>
+          <t>554095; 605132</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>542568; 593612</t>
+          <t>540583; 593540</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>862880; 912709</t>
+          <t>743433; 774809</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>841050; 912328</t>
+          <t>841699; 909353</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1038974; 1117099</t>
+          <t>1039305; 1114202</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1026538; 1102487</t>
+          <t>1030559; 1104401</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1505938; 1571935</t>
+          <t>1484693; 1530852</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>864395</t>
+          <t>924895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1046802</t>
+          <t>1067051</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1911197</t>
+          <t>1991946</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>548387; 607610</t>
+          <t>546313; 605049</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>657395; 712519</t>
+          <t>658229; 715730</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>684311; 736282</t>
+          <t>682473; 735084</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>844899; 879199</t>
+          <t>905046; 939997</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>687044; 747333</t>
+          <t>687543; 746912</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>847516; 898912</t>
+          <t>845566; 896105</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>829611; 879934</t>
+          <t>832705; 881146</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1031749; 1058642</t>
+          <t>1052399; 1079610</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1253070; 1337945</t>
+          <t>1255933; 1339036</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1518096; 1593098</t>
+          <t>1521826; 1596873</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1530736; 1605396</t>
+          <t>1532710; 1600732</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1887117; 1931827</t>
+          <t>1970357; 2011606</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3263898</t>
+          <t>3329251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3508214</t>
+          <t>3571959</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6772113</t>
+          <t>6901209</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2013745; 2128375</t>
+          <t>2020508; 2125928</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2376920; 2486475</t>
+          <t>2378762; 2487264</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2389348; 2491913</t>
+          <t>2392468; 2498647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3225292; 3308458</t>
+          <t>3298351; 3361511</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2341215; 2449848</t>
+          <t>2344836; 2451375</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2772253; 2868338</t>
+          <t>2770591; 2869215</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2683182; 2780348</t>
+          <t>2676208; 2778115</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3481519; 3538720</t>
+          <t>3547249; 3595058</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4397999; 4555090</t>
+          <t>4385114; 4542259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5181387; 5330806</t>
+          <t>5183933; 5328090</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5097210; 5246277</t>
+          <t>5092834; 5239708</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6717872; 6824431</t>
+          <t>6856932; 6937159</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36B08_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36B08_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas (tasa de respuesta: 99,79%)</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas (tasa de respuesta: 99,79%)</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
